--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원흥 메이저리티 PT 스튜디오</t>
+          <t>무브짐24시헬스PT 화정점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>majority-pt-studio@naver.com</t>
+          <t>move2829@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1399-1794</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>경기 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/majority-pt-studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fedk</t>
+          <t>https://talk.naver.com/ct/wsgemoy</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>88</v>
+        <v>2312</v>
       </c>
       <c r="Q2" t="n">
-        <v>125</v>
+        <v>741</v>
       </c>
       <c r="R2" t="n">
-        <v>213</v>
+        <v>3053</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1407985314</t>
+          <t>1146724512</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407985314</t>
+          <t>https://m.place.naver.com/place/1146724512</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
+          <t>https://talk.naver.com/ct/w5tj13</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1209</v>
+        <v>1242</v>
       </c>
       <c r="Q3" t="n">
-        <v>1612</v>
+        <v>1085</v>
       </c>
       <c r="R3" t="n">
-        <v>2821</v>
+        <v>2327</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>무브짐24시헬스PT 화정점</t>
+          <t>1986피트니스 헬스PT 지축점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>move2829@naver.com</t>
+          <t>1986fitness6@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1399-1794</t>
+          <t>0507-1304-2474</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 백양로 65 201호</t>
+          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/movegym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsgemoy</t>
+          <t>https://talk.naver.com/ct/w45al9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2278</v>
+        <v>1021</v>
       </c>
       <c r="Q4" t="n">
-        <v>718</v>
+        <v>1005</v>
       </c>
       <c r="R4" t="n">
-        <v>2996</v>
+        <v>2026</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1146724512</t>
+          <t>1814490801</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146724512</t>
+          <t>https://m.place.naver.com/place/1814490801</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>1986피트니스 헬스PT 원흥점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>1986fitness2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1370-1986</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
+          <t>경기 고양시 덕양구 삼송로 12 10층 1001호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
+          <t>https://talk.naver.com/ct/w40tzm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1228</v>
+        <v>1679</v>
       </c>
       <c r="Q5" t="n">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="R5" t="n">
-        <v>2310</v>
+        <v>2768</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1924563634</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1924563634</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zymk</t>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>558</v>
+        <v>1346</v>
       </c>
       <c r="Q6" t="n">
-        <v>895</v>
+        <v>327</v>
       </c>
       <c r="R6" t="n">
-        <v>1453</v>
+        <v>1673</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1054,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 지축점</t>
+          <t>원흥 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1986fitness6@naver.com</t>
+          <t>majority-pt-studio@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1304-2474</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness6</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45al9</t>
+          <t>https://talk.naver.com/ct/w4fedk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1019</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>993</v>
+        <v>127</v>
       </c>
       <c r="R7" t="n">
-        <v>2012</v>
+        <v>218</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1814490801</t>
+          <t>1407985314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814490801</t>
+          <t>https://m.place.naver.com/place/1407985314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>MTO 피트니스 PT 정발산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>jbsfitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1467-8389</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
+          <t>https://talk.naver.com/ct/w4f6xw</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1322</v>
+        <v>429</v>
       </c>
       <c r="Q8" t="n">
-        <v>293</v>
+        <v>728</v>
       </c>
       <c r="R8" t="n">
-        <v>1615</v>
+        <v>1157</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1314564243</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1314564243</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,95 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>7593168</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7593168</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>7209147</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7209147</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 백양로 65 201호</t>
+          <t>경기도 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/movegym24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsgemoy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2312</v>
+        <v>2320</v>
       </c>
       <c r="Q2" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="R2" t="n">
-        <v>3053</v>
+        <v>3068</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>1986피트니스 헬스PT 지축점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>1986fitness6@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1304-2474</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/1986fitness6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1242</v>
+        <v>1021</v>
       </c>
       <c r="Q3" t="n">
-        <v>1085</v>
+        <v>1002</v>
       </c>
       <c r="R3" t="n">
-        <v>2327</v>
+        <v>2023</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1814490801</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1814490801</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 지축점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1986fitness6@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1304-2474</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45al9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1021</v>
+        <v>1353</v>
       </c>
       <c r="Q4" t="n">
-        <v>1005</v>
+        <v>337</v>
       </c>
       <c r="R4" t="n">
-        <v>2026</v>
+        <v>1690</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1814490801</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814490801</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 원흥점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1986fitness2@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1370-1986</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 삼송로 12 10층 1001호</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40tzm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1679</v>
+        <v>1248</v>
       </c>
       <c r="Q5" t="n">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="R5" t="n">
-        <v>2768</v>
+        <v>2335</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1924563634</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924563634</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>1986피트니스 헬스PT 원흥점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>1986fitness2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1370-1986</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 덕양구 삼송로 12 10층 1001호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://blog.naver.com/1986fitness2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1346</v>
+        <v>1679</v>
       </c>
       <c r="Q6" t="n">
-        <v>327</v>
+        <v>1091</v>
       </c>
       <c r="R6" t="n">
-        <v>1673</v>
+        <v>2770</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,57 +1012,61 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1924563634</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1924563634</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원흥 메이저리티 PT 스튜디오</t>
+          <t>DOM 피트니스 PT 향동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>majority-pt-studio@naver.com</t>
+          <t>dom2051@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1335-0845</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>경기도 고양시 덕양구 향기로 115 8층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_QuxopG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,17 +1076,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fedk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>731</v>
       </c>
       <c r="Q7" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="R7" t="n">
-        <v>218</v>
+        <v>873</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1106,47 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1407985314</t>
+          <t>1049865238</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407985314</t>
+          <t>https://m.place.naver.com/place/1049865238</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MTO 피트니스 PT 정발산점</t>
+          <t>원흥 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jbsfitness@naver.com</t>
+          <t>majority-pt-studio@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1467-8389</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
+          <t>경기도 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/majority-pt-studio</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1156,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f6xw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>429</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="n">
-        <v>728</v>
+        <v>127</v>
       </c>
       <c r="R8" t="n">
-        <v>1157</v>
+        <v>218</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1314564243</t>
+          <t>1407985314</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314564243</t>
+          <t>https://m.place.naver.com/place/1407985314</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1284,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1362,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 백양로 65 201호</t>
+          <t>경기 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsgemoy</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45al9</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +824,10 @@
         <v>1353</v>
       </c>
       <c r="Q4" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="R4" t="n">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="Q5" t="n">
         <v>1087</v>
       </c>
       <c r="R5" t="n">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 삼송로 12 10층 1001호</t>
+          <t>경기 고양시 덕양구 삼송로 12 10층 1001호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40tzm</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1020,10 @@
         <v>1679</v>
       </c>
       <c r="Q6" t="n">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="R6" t="n">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 향기로 115 8층</t>
+          <t>경기 고양시 덕양구 향기로 115 8층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u2l4</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1141,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1166,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fedk</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 백양로 65 201호</t>
+          <t>경기도 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsgemoy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="Q2" t="n">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>3068</v>
+        <v>3081</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 지축점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1986fitness6@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1304-2474</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness6</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45al9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1021</v>
+        <v>1353</v>
       </c>
       <c r="Q3" t="n">
-        <v>1002</v>
+        <v>341</v>
       </c>
       <c r="R3" t="n">
-        <v>2023</v>
+        <v>1694</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1814490801</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814490801</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,19 +789,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1353</v>
+        <v>1251</v>
       </c>
       <c r="Q4" t="n">
-        <v>340</v>
+        <v>1089</v>
       </c>
       <c r="R4" t="n">
-        <v>1693</v>
+        <v>2340</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>1986피트니스 헬스PT 지축점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>1986fitness6@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1304-2474</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>https://blog.naver.com/1986fitness6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1249</v>
+        <v>1022</v>
       </c>
       <c r="Q5" t="n">
-        <v>1087</v>
+        <v>1005</v>
       </c>
       <c r="R5" t="n">
-        <v>2336</v>
+        <v>2027</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1814490801</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1814490801</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 삼송로 12 10층 1001호</t>
+          <t>경기도 고양시 덕양구 삼송로 12 10층 1001호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40tzm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="Q6" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="R6" t="n">
-        <v>2771</v>
+        <v>2774</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1049,39 +1029,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOM 피트니스 PT 향동점</t>
+          <t>원흥 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dom2051@naver.com</t>
+          <t>majority-pt-studio@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1335-0845</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 향기로 115 8층</t>
+          <t>경기도 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_QuxopG</t>
+          <t>https://blog.naver.com/majority-pt-studio</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,22 +1067,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u2l4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>731</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="R7" t="n">
-        <v>873</v>
+        <v>218</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1049865238</t>
+          <t>1407985314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049865238</t>
+          <t>https://m.place.naver.com/place/1407985314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1145,32 +1117,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>원흥 메이저리티 PT 스튜디오</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>majority-pt-studio@naver.com</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/majority-pt-studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1140,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fedk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,17 +1161,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1180,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1407985314</t>
+          <t>7593168</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407985314</t>
+          <t>https://m.place.naver.com/place/7593168</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1302,93 +1258,15 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7593168</t>
+          <t>7209147</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7593168</t>
+          <t>https://m.place.naver.com/place/7209147</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>7209147</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7209147</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="Q2" t="n">
         <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>3081</v>
+        <v>3091</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="Q6" t="n">
         <v>1094</v>
       </c>
       <c r="R6" t="n">
-        <v>2774</v>
+        <v>2776</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1022,37 +1022,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원흥 메이저리티 PT 스튜디오</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>majority-pt-studio@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/majority-pt-studio</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>1221</v>
       </c>
       <c r="Q7" t="n">
-        <v>127</v>
+        <v>1612</v>
       </c>
       <c r="R7" t="n">
-        <v>218</v>
+        <v>2833</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1407985314</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407985314</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1194,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -718,10 +718,10 @@
         <v>1353</v>
       </c>
       <c r="Q3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R3" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>1251</v>
       </c>
       <c r="Q4" t="n">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="R4" t="n">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>1022</v>
       </c>
       <c r="Q5" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="R5" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1029,34 +1029,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>원흥 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>majority-pt-studio@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1348-8027</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://blog.naver.com/majority-pt-studio</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1221</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>1612</v>
+        <v>127</v>
       </c>
       <c r="R7" t="n">
-        <v>2833</v>
+        <v>218</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1407985314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1407985314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1121,20 +1117,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1144,12 +1156,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1165,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1221</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1612</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2833</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7593168</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7593168</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1262,15 +1274,93 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>7593168</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7593168</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>7209147</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7209147</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 백양로 65 201호</t>
+          <t>경기 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsgemoy</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="Q3" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="R3" t="n">
-        <v>1695</v>
+        <v>1701</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="Q4" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="R4" t="n">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45al9</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -906,10 +922,10 @@
         <v>1022</v>
       </c>
       <c r="Q5" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="R5" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 삼송로 12 10층 1001호</t>
+          <t>경기 고양시 덕양구 삼송로 12 10층 1001호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40tzm</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1020,10 @@
         <v>1682</v>
       </c>
       <c r="Q6" t="n">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="R6" t="n">
-        <v>2776</v>
+        <v>2782</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1047,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1072,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fedk</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1090,10 +1114,10 @@
         <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1141,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1166,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/고양_PT.xlsx
+++ b/naver-place-crawler/results_health/고양_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 백양로 65 201호</t>
+          <t>경기도 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsgemoy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="Q2" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="R2" t="n">
-        <v>3091</v>
+        <v>3093</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="Q3" t="n">
         <v>346</v>
       </c>
       <c r="R3" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -846,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기도 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45al9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -922,10 +906,10 @@
         <v>1022</v>
       </c>
       <c r="Q5" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="R5" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 삼송로 12 10층 1001호</t>
+          <t>경기도 고양시 덕양구 삼송로 12 10층 1001호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40tzm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1042,37 +1022,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원흥 메이저리티 PT 스튜디오</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>majority-pt-studio@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 덕양구 원흥1로 58 4층 메이저리티 PT 스튜디오</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/majority-pt-studio</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1092,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fedk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>1222</v>
       </c>
       <c r="Q7" t="n">
-        <v>128</v>
+        <v>1612</v>
       </c>
       <c r="R7" t="n">
-        <v>219</v>
+        <v>2834</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1106,35 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1407985314</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407985314</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5150피트니스 일산 대화점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5150fitness2@naver.com</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1348-8027</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1144,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,17 +1165,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1612</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2833</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>7593168</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/7593168</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1302,95 +1262,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7593168</t>
+          <t>7209147</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7593168</t>
+          <t>https://m.place.naver.com/place/7209147</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>7209147</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7209147</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
